--- a/stories/arbres/ATOM-SOC.TRA.001-04.xlsx
+++ b/stories/arbres/ATOM-SOC.TRA.001-04.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Papa et Hortense vont à la gare. Hortense tient la main de papa. Ils restent avec un adulte. Papa, c'est l'adulte. Un train arrive. Le train fait tchou tchou. Papa dit : c'est un train. C'est le nom du véhicule. Hortense répète : un train. Ils montent avec papa. Hortense s'assoit près de papa. Le train roule. Par la fenêtre, Hortense voit le ciel. Un avion passe. Papa dit : c'est un avion. C'est un autre nom de véhicule. Hortense dit : un avion. Plus loin, il y a une rivière. Un bateau glisse. Papa dit : c'est un bateau. Hortense dit : un bateau. Train, avion, bateau. Hortense nomme. Elle reste avec papa.</t>
+          <t>Papa et Hortense vont à la gare. Hortense tient la main de papa. Ils restent avec un adulte. Papa, c'est l'adulte. Un train arrive. Le train fait tchou tchou. C'est un train. C'est le nom du véhicule. Hortense répète : un train. Ils montent avec papa. Hortense s'assoit près de papa. Le train roule. Par la fenêtre, Hortense voit le ciel. Un avion passe. C'est un avion. C'est un autre nom de véhicule. Un avion. Plus loin, il y a une rivière. Un bateau glisse. C'est un bateau. Un bateau. Train, avion, bateau. Hortense nomme. Elle reste avec papa.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,19 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Papa et Hortense vont à la gare. Hortense tient la main de papa. Ils restent avec un adulte. Papa, c'est l'adulte. Un train arrive. Le train fait tchou tchou.
+papa|C'est un train. C'est le nom du véhicule.
+narrateur|Hortense répète : un train. Ils montent avec papa. Hortense s'assoit près de papa. Le train roule. Par la fenêtre, Hortense voit le ciel. Un avion passe.
+papa|C'est un avion. C'est un autre nom de véhicule.
+enfant-f|Un avion. Plus loin, il y a une rivière.
+narrateur|Un bateau glisse.
+papa|C'est un bateau.
+enfant-f|Un bateau. Train, avion, bateau.
+narrateur|Hortense nomme. Elle reste avec papa.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1469,6 +1498,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Hortense nomme un véhicule. Lequel ?</t>
         </is>
       </c>
     </row>
@@ -1637,6 +1671,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Hortense a dit le nom du véhicule. Train. Avion. Bateau. Elle est restée avec papa.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1799,6 +1838,11 @@
         <v>12</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Le train s'arrête. Hortense donne la main à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1961,6 +2005,11 @@
         <v>12</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1979,7 +2028,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1996,6 +2045,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SOC.TRA.001-04.xlsx
+++ b/stories/arbres/ATOM-SOC.TRA.001-04.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1318,6 +1323,7 @@
 narrateur|Hortense nomme. Elle reste avec papa.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1505,6 +1511,7 @@
           <t>narrateur|Hortense nomme un véhicule. Lequel ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1676,6 +1683,7 @@
           <t>narrateur|Hortense a dit le nom du véhicule. Train. Avion. Bateau. Elle est restée avec papa.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1843,6 +1851,7 @@
           <t>narrateur|Le train s'arrête. Hortense donne la main à papa.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2010,6 +2019,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2028,7 +2038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2052,6 +2062,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2066,7 +2090,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2253,6 +2277,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SOC.TRA.001-04.xlsx
+++ b/stories/arbres/ATOM-SOC.TRA.001-04.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Le train d'Hortense</t>
+          <t>Le goûter du train</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Amir veut manger son goûter dans le train. Ils montent. Une miette tombe. Il reste assis, près de papa.</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Papa et Hortense vont à la gare. Hortense tient la main de papa. Ils restent avec un adulte. Papa, c'est l'adulte. Un train arrive. Le train fait tchou tchou. C'est un train. C'est le nom du véhicule. Hortense répète : un train. Ils montent avec papa. Hortense s'assoit près de papa. Le train roule. Par la fenêtre, Hortense voit le ciel. Un avion passe. C'est un avion. C'est un autre nom de véhicule. Un avion. Plus loin, il y a une rivière. Un bateau glisse. C'est un bateau. Un bateau. Train, avion, bateau. Hortense nomme. Elle reste avec papa.</t>
+          <t>L'horloge de la gare fait tic. Ça sent l'huile et le pain. Le sac de papa est en toile. Le papier du goûter craque. Amir vit ici, avec papa. Tu as entendu l'horloge ? Elle fait tic. Oui. Le train arrive. En ce moment, le quai vibre. Un souffle chaud passe. C'est le train ? Oui. C'est le nom du véhicule. Un train. On monte avec un adulte. Ils montent avec papa. Amir s'assoit près de papa. Le siège est un peu dur. Le sac repose sur les genoux. Tu restes assis ? Oui, papa. Le train part tout doux. Les maisons glissent. On ouvre le goûter ? Oui ! Papa défait le papier. Ça sent le beurre tiède. Une madeleine ! Une petite. Amir croque, assis. Une miette tombe. La miette reste sur le siège. Oh. Tu la prends, assis ? Oui. Amir la prend, tout doux. Il reste près de papa. Le papier craque encore un peu. Tu bois une gorgée ? Oui. La gourde est fraîche. L'eau sent le plastique. Amir remet le bouchon, assis. On garde le papier ? Pour les miettes. Une autre miette attend. Amir la pose dans le papier. Le wagon fait un long souffle. Tu vois les arbres ? Ils courent. Nous, on reste assis.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Papa et Hortense vont à la gare. Hortense tient la main de papa. Ils restent avec un adulte. Papa, c'est l'adulte. Un train arrive. Le train fait tchou tchou. Papa dit : c'est un train. C'est le &lt;emphasis level="moderate"&gt;nom&lt;/emphasis&gt; du véhicule. Hortense répète : un train. Ils montent avec papa. Hortense s'assoit près de papa. Le train roule. Par la fenêtre, Hortense voit le ciel. Un avion passe. Papa dit : c'est un avion. C'est un autre nom de véhicule. Hortense dit : un avion. Plus loin, il y a une rivière. Un bateau glisse. Papa dit : c'est un bateau. Hortense dit : un bateau. Train, avion, bateau. Hortense nomme. Elle reste avec papa.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>L'horloge de la gare fait tic. Ça sent l'huile et le pain. Le sac de papa est en toile. Le papier du goûter craque. Amir vit ici, avec papa. Tu as entendu l'horloge ? Elle fait tic. Oui. Le train arrive. En ce moment, le quai vibre. Un souffle chaud passe. C'est le train ? Oui. C'est le nom du véhicule. Un train. On monte avec un adulte. Ils montent avec papa. Amir s'assoit près de papa. Le siège est un peu dur. Le sac repose sur les genoux. Tu restes assis ? Oui, papa. Le train part tout doux. Les maisons glissent. On ouvre le goûter ? Oui ! Papa défait le papier. Ça sent le beurre tiède. Une madeleine ! Une petite. Amir croque, assis. Une miette tombe. La miette reste sur le siège. Oh. Tu la prends, assis ? Oui. Amir la prend, tout doux. Il reste près de papa. Le papier craque encore un peu. Tu bois une gorgée ? Oui. La gourde est fraîche. L'eau sent le plastique. Amir remet le bouchon, assis. On garde le papier ? Pour les miettes. Une autre miette attend. Amir la pose dans le papier. Le wagon fait un long souffle. Tu vois les arbres ? Ils courent. Nous, on reste assis.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1233,14 +1245,14 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA2" s="2" t="n">
         <v>0.86</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1312,18 +1324,60 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Papa et Hortense vont à la gare. Hortense tient la main de papa. Ils restent avec un adulte. Papa, c'est l'adulte. Un train arrive. Le train fait tchou tchou.
-papa|C'est un train. C'est le nom du véhicule.
-narrateur|Hortense répète : un train. Ils montent avec papa. Hortense s'assoit près de papa. Le train roule. Par la fenêtre, Hortense voit le ciel. Un avion passe.
-papa|C'est un avion. C'est un autre nom de véhicule.
-enfant-f|Un avion. Plus loin, il y a une rivière.
-narrateur|Un bateau glisse.
-papa|C'est un bateau.
-enfant-f|Un bateau. Train, avion, bateau.
-narrateur|Hortense nomme. Elle reste avec papa.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|L'horloge de la gare fait tic.
+narrateur|Ça sent l'huile et le pain.
+narrateur|Le sac de papa est en toile.
+narrateur|Le papier du goûter craque.
+narrateur|Amir vit ici, avec papa.
+papa|Tu as entendu l'horloge ?
+enfant-m|Elle fait tic.
+papa|Oui.
+papa|Le train arrive.
+narrateur|En ce moment, le quai vibre.
+narrateur|Un souffle chaud passe.
+enfant-m|C'est le train ?
+papa|Oui.
+papa|C'est le nom du véhicule.
+enfant-m|Un train.
+papa|On monte avec un adulte.
+narrateur|Ils montent avec papa.
+narrateur|Amir s'assoit près de papa.
+narrateur|Le siège est un peu dur.
+narrateur|Le sac repose sur les genoux.
+papa|Tu restes assis ?
+enfant-m|Oui, papa.
+narrateur|Le train part tout doux.
+narrateur|Les maisons glissent.
+papa|On ouvre le goûter ?
+enfant-m|Oui !
+narrateur|Papa défait le papier.
+narrateur|Ça sent le beurre tiède.
+enfant-m|Une madeleine !
+papa|Une petite.
+narrateur|Amir croque, assis.
+narrateur|Une miette tombe.
+narrateur|La miette reste sur le siège.
+enfant-m|Oh.
+papa|Tu la prends, assis ?
+enfant-m|Oui.
+narrateur|Amir la prend, tout doux.
+narrateur|Il reste près de papa.
+narrateur|Le papier craque encore un peu.
+papa|Tu bois une gorgée ?
+enfant-m|Oui.
+narrateur|La gourde est fraîche.
+narrateur|L'eau sent le plastique.
+narrateur|Amir remet le bouchon, assis.
+papa|On garde le papier ?
+enfant-m|Pour les miettes.
+narrateur|Une autre miette attend.
+narrateur|Amir la pose dans le papier.
+narrateur|Le wagon fait un long souffle.
+papa|Tu vois les arbres ?
+enfant-m|Ils courent.
+papa|Nous, on reste assis.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1348,12 +1402,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Hortense nomme un véhicule. Lequel ?</t>
+          <t>Amir nomme le véhicule. Lequel ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Hortense &lt;emphasis level="moderate"&gt;nom&lt;/emphasis&gt;me un véhicule. Lequel ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Amir nomme le véhicule. Lequel ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1368,7 +1422,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>train | avion | bateau | un train</t>
+          <t>train | un train | le train | avion | bateau</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1383,7 +1437,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Elle a vu un train. Quel véhicule ?</t>
+          <t>Il a pris le train. Quel véhicule ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1432,7 +1486,7 @@
         <v>0.8</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1508,10 +1562,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Hortense nomme un véhicule. Lequel ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Amir nomme le véhicule.
+narrateur|Lequel ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1536,12 +1590,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Hortense a dit le nom du véhicule. Train. Avion. Bateau. Elle est restée avec papa.</t>
+          <t>Par la fenêtre, le ciel est bleu. Un trait blanc traverse. Tu vois ça ? Un avion. Oui. C'est un avion. Plus loin, une rivière brille. Un bateau glisse, tout petit. Et ça ? Un bateau. Bravo. Amir mâche encore. La madeleine est douce. Le papier repose sur le sac. Tu restes assis ? Oui. Ses pieds touchent le plancher. Le wagon fait un petit toc. Amir plie le papier. Les miettes restent dedans. Tu as encore faim ? Un peu. On garde une miette. Amir sourit, assis. Le ciel file tout bleu. Un oiseau suit le train. Il vole vite. Oui. Toi, tu restes ici.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Hortense a dit le &lt;emphasis level="moderate"&gt;nom&lt;/emphasis&gt; du véhicule. Train. Avion. Bateau. Elle est restée avec papa.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Par la fenêtre, le ciel est bleu. Un trait blanc traverse. Tu vois ça ? Un avion. Oui. C'est un avion. Plus loin, une rivière brille. Un bateau glisse, tout petit. Et ça ? Un bateau. Bravo. Amir mâche encore. La madeleine est douce. Le papier repose sur le sac. Tu restes assis ? Oui. Ses pieds touchent le plancher. Le wagon fait un petit toc. Amir plie le papier. Les miettes restent dedans. Tu as encore faim ? Un peu. On garde une miette. Amir sourit, assis. Le ciel file tout bleu. Un oiseau suit le train. Il vole vite. Oui. Toi, tu restes ici.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1597,14 +1651,14 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA4" s="2" t="n">
         <v>0.86</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1680,10 +1734,37 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Hortense a dit le nom du véhicule. Train. Avion. Bateau. Elle est restée avec papa.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Par la fenêtre, le ciel est bleu.
+narrateur|Un trait blanc traverse.
+papa|Tu vois ça ?
+enfant-m|Un avion.
+papa|Oui.
+papa|C'est un avion.
+narrateur|Plus loin, une rivière brille.
+narrateur|Un bateau glisse, tout petit.
+papa|Et ça ?
+enfant-m|Un bateau.
+papa|Bravo.
+narrateur|Amir mâche encore.
+narrateur|La madeleine est douce.
+narrateur|Le papier repose sur le sac.
+papa|Tu restes assis ?
+enfant-m|Oui.
+narrateur|Ses pieds touchent le plancher.
+narrateur|Le wagon fait un petit toc.
+narrateur|Amir plie le papier.
+narrateur|Les miettes restent dedans.
+papa|Tu as encore faim ?
+enfant-m|Un peu.
+papa|On garde une miette.
+narrateur|Amir sourit, assis.
+narrateur|Le ciel file tout bleu.
+narrateur|Un oiseau suit le train.
+enfant-m|Il vole vite.
+papa|Oui.
+papa|Toi, tu restes ici.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1708,12 +1789,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Le train s'arrête. Hortense donne la main à papa.</t>
+          <t>Le train ralentit. Les maisons redeviennent grandes. On arrive. On reste assis encore. D'accord. Amir tient le papier vide. Le train s'arrête. Maintenant on se lève. Ils se lèvent ensemble. Amir donne la main à papa. Tu as mangé assis. C'était bon.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Le train s'arrête. Hortense donne la &lt;emphasis level="moderate"&gt;main&lt;/emphasis&gt; à papa.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le train ralentit. Les maisons redeviennent grandes. On arrive. On reste assis encore. D'accord. Amir tient le papier vide. Le train s'arrête. Maintenant on se lève. Ils se lèvent ensemble. Amir donne la main à papa. Tu as mangé assis. C'était bon.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1769,14 +1850,14 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA5" s="2" t="n">
         <v>0.86</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1848,10 +1929,20 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Le train s'arrête. Hortense donne la main à papa.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Le train ralentit.
+narrateur|Les maisons redeviennent grandes.
+papa|On arrive.
+papa|On reste assis encore.
+enfant-m|D'accord.
+narrateur|Amir tient le papier vide.
+narrateur|Le train s'arrête.
+papa|Maintenant on se lève.
+narrateur|Ils se lèvent ensemble.
+narrateur|Amir donne la main à papa.
+papa|Tu as mangé assis.
+enfant-m|C'était bon.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1876,12 +1967,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Sur le quai, l'air sent le pain. Le train est arrêté. Oui. Une miette reste dans le papier. Amir la garde dans la main.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Sur le quai, l'air sent le pain. Le train est arrêté. Oui. Une miette reste dans le papier. Amir la garde dans la main.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1937,14 +2028,14 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA6" s="2" t="n">
         <v>0.82</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2016,10 +2107,13 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>narrateur|Sur le quai, l'air sent le pain.
+enfant-m|Le train est arrêté.
+papa|Oui.
+narrateur|Une miette reste dans le papier.
+narrateur|Amir la garde dans la main.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2038,7 +2132,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2076,6 +2170,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SOC.TRA.001-04.xlsx
+++ b/stories/arbres/ATOM-SOC.TRA.001-04.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>gare et train</t>
+          <t>gare puis wagon, après-midi</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Hortense, papa</t>
+          <t>Amir, papa</t>
         </is>
       </c>
     </row>
